--- a/p6_deployment/data/france/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/p6_deployment/data/france/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,662 +475,545 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_home</t>
+          <t>id_country</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>coach_home</t>
+          <t>id_competition</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_away</t>
+          <t>is_cup</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>coach_away</t>
+          <t>season</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>id_country</t>
+          <t>country</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>id_competition</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>is_cup</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>season</t>
+          <t>competition</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>88K4TzrO</t>
+          <t>2NocJFqd</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45431.66666666666</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stinat j   fra </t>
-        </is>
-      </c>
+        <v>45522.5</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade oceane  le havre </t>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>25178</v>
+        <v>18752</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>marseille</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>25Wk0Fko</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>elsner luka</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>EgvyJSJo</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>gasset jean louis</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
+          <t>lens</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>55</v>
       </c>
-      <c r="O2" t="n">
+      <c r="K2" t="n">
         <v>551</v>
       </c>
-      <c r="P2" t="n">
+      <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>20232024</v>
+      <c r="M2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2ek4VdDB</t>
+          <t>ripawyyS</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45431.66666666666</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">leonard t   fra </t>
-        </is>
-      </c>
+        <v>45522.5</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade bollaert delelis  lens </t>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>38223</v>
+        <v>17924</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>lens</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>montpellier</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>d0X3cO3I</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>haise franck</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>vVQcGxl1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>der zakarian michel</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>55</v>
       </c>
-      <c r="O3" t="n">
+      <c r="K3" t="n">
         <v>551</v>
       </c>
-      <c r="P3" t="n">
+      <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>20232024</v>
+      <c r="M3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>naJ8SfcU</t>
+          <t>0js8u60b</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45431.66666666666</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">delajod w   fra </t>
-        </is>
-      </c>
+        <v>45522.5</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade pierre mauroy  villeneuve d ascq </t>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>50186</v>
+        <v>15220</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>lille</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>nice</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>KAwSWnoE</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fonseca paulo</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>zuUcoUwO</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>farioli francesco</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
+          <t>marseille</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>55</v>
       </c>
-      <c r="O4" t="n">
+      <c r="K4" t="n">
         <v>551</v>
       </c>
-      <c r="P4" t="n">
+      <c r="L4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>20232024</v>
+      <c r="M4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8Yk0Wxb5</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45431.66666666666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">turpin c   fra </t>
-        </is>
-      </c>
+        <v>45522.5</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade du moustoir  lorient </t>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16787</v>
+        <v>25178</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>jgNAYRGi</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>lorient</t>
+          <t>le havre</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>IRuMRua1</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>clermont</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>pYaUUJs1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>le bris regis</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>OYUbATyb</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gastien pascal</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
+          <t>psg</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>55</v>
       </c>
-      <c r="O5" t="n">
+      <c r="K5" t="n">
         <v>551</v>
       </c>
-      <c r="P5" t="n">
+      <c r="L5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>20232024</v>
+      <c r="M5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>xObInbrn</t>
+          <t>fHYrsJy3</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45431.66666666666</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wattellier e   fra </t>
-        </is>
-      </c>
+        <v>45522.5</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc olympique lyonnais  lyon </t>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>59186</v>
+        <v>18523</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>lyon</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>strasbourg</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>sage pierre</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>AaLVdEGK</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>vieira patrick</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
+          <t>st etienne</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>55</v>
       </c>
-      <c r="O6" t="n">
+      <c r="K6" t="n">
         <v>551</v>
       </c>
-      <c r="P6" t="n">
+      <c r="L6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>20232024</v>
+      <c r="M6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>OKfEmvTu</t>
+          <t>M5VGwpVA</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45431.66666666666</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">angoula g   fra </t>
-        </is>
-      </c>
+        <v>45522.5</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade saint symphorien  metz </t>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>28786</v>
+        <v>20484</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>4v0yqlWc</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>metz</t>
+          <t>montpellier</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>psg</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>KYsw3uKl</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>boloni laszlo</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>8MdrBIUb</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>luis enrique</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
+          <t>strasbourg</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
         <v>55</v>
       </c>
-      <c r="O7" t="n">
+      <c r="K7" t="n">
         <v>551</v>
       </c>
-      <c r="P7" t="n">
+      <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>20232024</v>
+      <c r="M7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>tnl8UGSH</t>
+          <t>jqSiuc6F</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45431.66666666666</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lissorgue r   fra </t>
-        </is>
-      </c>
+        <v>45522.5</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade louis ii  monaco </t>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>18523</v>
+        <v>21029</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>reims</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>nantes</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>CWxpUrtf</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>hutter adi</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>YTLwacK1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>kombouare antoine</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
+          <t>lille</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
         <v>55</v>
       </c>
-      <c r="O8" t="n">
+      <c r="K8" t="n">
         <v>551</v>
       </c>
-      <c r="P8" t="n">
+      <c r="L8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>20232024</v>
+      <c r="M8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>fVodXIra</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45431.66666666666</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vernice m   fra </t>
-        </is>
-      </c>
+        <v>45522.5</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade auguste delaune  reims </t>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>21029</v>
+        <v>29778</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>reims</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>rennes</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>SIFtcwDc</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>diawara samba</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>stephan julien</t>
-        </is>
-      </c>
-      <c r="N9" t="n">
+          <t>lyon</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
         <v>55</v>
       </c>
-      <c r="O9" t="n">
+      <c r="K9" t="n">
         <v>551</v>
       </c>
-      <c r="P9" t="n">
+      <c r="L9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>20232024</v>
+      <c r="M9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>C6diYbTh</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45431.66666666666</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pignard j   fra </t>
-        </is>
-      </c>
+        <v>45522.5</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadium municipal  toulouse </t>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1148,45 +1031,35 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>brest</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>UapruDaf</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>martinez carles</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>0tIbS515</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>roy eric</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
+          <t>nantes</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
         <v>55</v>
       </c>
-      <c r="O10" t="n">
+      <c r="K10" t="n">
         <v>551</v>
       </c>
-      <c r="P10" t="n">
+      <c r="L10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>20232024</v>
+      <c r="M10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
       </c>
     </row>
   </sheetData>
